--- a/output/pdf_financials_xlsx/NHHH.xlsx
+++ b/output/pdf_financials_xlsx/NHHH.xlsx
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.2914</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.215275</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.0408</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.032001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.019535</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.015059</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -1116,16 +1116,16 @@
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.028487</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.027722</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.008094</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.004662</v>
       </c>
     </row>
     <row r="13">
@@ -2079,22 +2079,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.738623</v>
+        <v>-8.030023</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-10.089127</v>
+        <v>-10.304402</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-6.246972</v>
+        <v>-6.287772</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.498702</v>
+        <v>-4.530703</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.615077</v>
+        <v>-1.634612</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.615077</v>
+        <v>-1.630136</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -2122,16 +2122,16 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-14.299626</v>
+        <v>-14.328113</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-13.123111</v>
+        <v>-13.150833</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-19.122302</v>
+        <v>-19.130396</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-4.778476</v>
+        <v>-4.783138</v>
       </c>
     </row>
     <row r="28">
@@ -2201,22 +2201,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.738623</v>
+        <v>-8.030023</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-10.089127</v>
+        <v>-10.304402</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-6.246972</v>
+        <v>-6.287772</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.498702</v>
+        <v>-4.530703</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.615077</v>
+        <v>-1.634612</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.613514</v>
+        <v>-1.628573</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-12.484905</v>
+        <v>-12.513392</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-10.595292</v>
+        <v>-10.623014</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-16.307469</v>
+        <v>-16.315563</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.005645</v>
+        <v>-2.010307</v>
       </c>
     </row>
     <row r="30">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-254.2333107526974</v>
+        <v>-263.8065367327375</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-722.8038187976776</v>
+        <v>-738.2265200969745</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -2517,31 +2517,31 @@
         <v>0.474452</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.915165</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.322569</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.700824</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.998181</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.018602</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.433749</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.01942</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.648034</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.003115</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>5.257352</v>
@@ -2633,31 +2633,31 @@
         <v>5.074652</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.765</v>
+        <v>1.680165</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.615023</v>
+        <v>1.937592</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.015045</v>
+        <v>0.715869</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.015</v>
+        <v>1.013181</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.012</v>
+        <v>0.030602</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.005</v>
+        <v>1.438749</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.01942</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.648034</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.003115</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>5.257352</v>
@@ -3329,31 +3329,31 @@
         <v>0.34714</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.182022</v>
+        <v>0.266857</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.479254</v>
+        <v>0.156685</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.875063</v>
+        <v>0.174239</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.167596</v>
+        <v>0.169415</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.177108</v>
+        <v>0.158506</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.602567</v>
+        <v>0.168818</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.36255</v>
+        <v>0.34313</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.960364</v>
+        <v>0.31233</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.519574</v>
+        <v>0.516459</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.230776</v>
@@ -7860,16 +7860,16 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.063891</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.021938</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.240589</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.145925</v>
       </c>
     </row>
     <row r="125">
@@ -7918,16 +7918,16 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.063891</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.021938</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.240589</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.145925</v>
       </c>
     </row>
     <row r="126">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -15304,7 +15304,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -17856,7 +17856,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -23556,7 +23556,11 @@
           <t>Lease payments (note 13)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -30209,7 +30213,11 @@
           <t>Lease payments (note 14)</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -44924,7 +44932,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -45611,7 +45619,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -48013,7 +48021,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E398" s="5" t="n">

--- a/output/pdf_financials_xlsx/NHHH.xlsx
+++ b/output/pdf_financials_xlsx/NHHH.xlsx
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.015643</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.000125</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.00135</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.001392</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.011234</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -7589,10 +7589,10 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>15.520871</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>8.476145000000001</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>4.677045</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>0</v>
@@ -31116,7 +31116,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -35088,7 +35092,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -37256,7 +37264,11 @@
           <t>Issuance of shares, net of issuance costs 11</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -38060,7 +38072,11 @@
           <t>Proceeds on disposal of property and equipment 6</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -41700,7 +41716,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -44324,7 +44344,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E361" s="5" t="n">
         <v>15.520871</v>
       </c>

--- a/output/pdf_financials_xlsx/NHHH.xlsx
+++ b/output/pdf_financials_xlsx/NHHH.xlsx
@@ -1632,27 +1632,29 @@
         <v>-7.738623</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-10.089127</v>
+        <v>-4.687097</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-6.246972</v>
+        <v>-4.141528</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-4.498702</v>
+        <v>-4.114331</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-1.615077</v>
+        <v>-1.528425</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-1.615077</v>
+        <v>-1.625542</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>-10.13419</v>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="3" t="n">
         <v>-3.232515</v>
@@ -1694,16 +1696,16 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-5.40203</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-2.105444</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-0.384371</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.154532</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -1714,7 +1716,7 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-0.019887</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
@@ -1832,10 +1834,8 @@
       <c r="G23" s="3" t="n">
         <v>-1.615077</v>
       </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H23" s="3" t="n">
+        <v>-3.173925</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-10.13419</v>
@@ -4316,22 +4316,22 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.031533</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.049811</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.007753</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.040326</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.06930699999999999</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.738912</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0</v>
@@ -4490,49 +4490,49 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.423899</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.253593</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.183153</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.322263</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.368985</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.122819</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.45969</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.157214</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.148254</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.202909</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.069276</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.64699</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.08500199999999999</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.084745</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.6427389999999999</v>
       </c>
     </row>
     <row r="68">
@@ -4697,16 +4697,16 @@
         <v>0</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.010403</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.058859</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.207981</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.098124</v>
       </c>
     </row>
     <row r="71">
@@ -4755,16 +4755,16 @@
         <v>0</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07040299999999999</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0.04</v>
+        <v>0.098859</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.207981</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.098124</v>
       </c>
     </row>
     <row r="72">
@@ -4990,13 +4990,13 @@
         <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.058859</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.207981</v>
+        <v>0</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>1.044409</v>
+        <v>0.946285</v>
       </c>
     </row>
     <row r="76">
@@ -5303,16 +5303,16 @@
         </is>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.005894388173984246</v>
+        <v>0.00627197251978661</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.003171996669785089</v>
+        <v>0.005406834078804379</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.02385231191007866</v>
+        <v>0.04051285847078739</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>0.00263687366722885</v>
+        <v>0.01520930280829608</v>
       </c>
     </row>
     <row r="81">
@@ -6369,18 +6369,16 @@
         <v>-4.498702</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-1.615077</v>
+        <v>-1.528425</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-1.615077</v>
-      </c>
-      <c r="H99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.625542</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>-3.173925</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-10.13419</v>
+        <v>-10.154077</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-3.232515</v>
@@ -7023,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.055639</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.054089</v>
       </c>
       <c r="L110" s="3" t="n">
         <v>0</v>
@@ -9853,7 +9851,11 @@
           <t>Lease liabilities (note 13)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -11961,7 +11963,11 @@
           <t>Lease liabilities (note 14)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -31619,7 +31625,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -33421,7 +33431,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -37369,7 +37383,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -50211,7 +50229,11 @@
           <t>Loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -50244,7 +50266,7 @@
         <v>-0.028</v>
       </c>
       <c r="L420" s="5" t="n">
-        <v>0.019887</v>
+        <v>-0.019887</v>
       </c>
       <c r="M420" t="inlineStr">
         <is>
@@ -60815,7 +60837,11 @@
           <t>Loss from discontinued operations 5,15</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E526" t="inlineStr">
         <is>
           <t>-</t>
@@ -62942,7 +62968,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
@@ -63041,7 +63071,11 @@
           <t>Loss from discontinued operations 4,14</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>-</t>
@@ -63847,7 +63881,11 @@
           <t>Loss from discontinued operations (Note 5)</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr"/>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E556" t="inlineStr">
         <is>
           <t>-</t>
